--- a/output/pdf_financials_xlsx/GOOD.xlsx
+++ b/output/pdf_financials_xlsx/GOOD.xlsx
@@ -431,6 +431,19 @@
   </sheetPr>
   <dimension ref="A1:K135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/GOOD.xlsx
+++ b/output/pdf_financials_xlsx/GOOD.xlsx
@@ -4610,37 +4610,37 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.034411</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.034411</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.034411</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.034411</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.034411</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.034411</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.034411</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.082165</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.40895</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>2.45382</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>2.466409</v>
       </c>
     </row>
     <row r="93">
@@ -7764,7 +7764,11 @@
           <t>Share-based payment reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -8541,7 +8545,11 @@
           <t>Share-based payment reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -10166,7 +10174,11 @@
           <t>Share-based payment reserve (Note 12)</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -14264,7 +14276,11 @@
           <t>Share-based Payments Reserve 34,411</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
@@ -15114,7 +15130,11 @@
           <t>Share-based Payments Reserve 34,411</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E117" s="5" t="n">
         <v>0.034411</v>
       </c>

--- a/output/pdf_financials_xlsx/GOOD.xlsx
+++ b/output/pdf_financials_xlsx/GOOD.xlsx
@@ -2176,37 +2176,37 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.217841</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.182358</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.155255</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.090529</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.167642</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.143282</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.158629</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.582654</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.500396</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.046146</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.029271</v>
       </c>
     </row>
     <row r="35">
@@ -2256,37 +2256,37 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.217841</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.182358</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.155255</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.090529</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.167642</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.143282</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.158629</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>1.582654</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.500396</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.046146</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.029271</v>
       </c>
     </row>
     <row r="37">
@@ -2736,31 +2736,31 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.231861</v>
+        <v>0.01402</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.184947</v>
+        <v>0.002589</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.157844</v>
+        <v>0.002589</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.108902</v>
+        <v>0.018373</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.175808</v>
+        <v>0.008166</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.163948</v>
+        <v>0.020666</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.179854</v>
+        <v>0.021225</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>2.026352</v>
+        <v>0.443698</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.527419</v>
+        <v>0.027023</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0</v>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -13688,7 +13688,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -14704,7 +14704,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -15818,7 +15818,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -16035,7 +16035,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -16542,7 +16542,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -16903,7 +16903,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E142" s="5" t="n">
